--- a/artfynd/A 42900-2021 artfynd.xlsx
+++ b/artfynd/A 42900-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134083568</v>
       </c>
       <c r="B2" t="n">
-        <v>57947</v>
+        <v>57954</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42900-2021 artfynd.xlsx
+++ b/artfynd/A 42900-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,256 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134137503</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58598</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103051</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rosenfink</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carpodacus erythrinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hallastigen, Mösseberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>414141</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6450644</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Friggeråker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erik Josefsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134137510</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57962</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hallastigen, Mösseberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>414141</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6450644</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Friggeråker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Josefsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42900-2021 artfynd.xlsx
+++ b/artfynd/A 42900-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134083568</v>
       </c>
       <c r="B2" t="n">
-        <v>57954</v>
+        <v>57964</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>134137503</v>
       </c>
       <c r="B3" t="n">
-        <v>58598</v>
+        <v>58608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>134137510</v>
       </c>
       <c r="B4" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42900-2021 artfynd.xlsx
+++ b/artfynd/A 42900-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1050,6 +1050,268 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134316906</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58061</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hallastigen, Mösseberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>414141</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6450644</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Friggeråker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Josefsson, Kim Roelofs</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134316896</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57860</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100100</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bivråk</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pernis apivorus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hallastigen, Mösseberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>414141</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6450644</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Friggeråker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Josefsson, Kim Roelofs</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42900-2021 artfynd.xlsx
+++ b/artfynd/A 42900-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134083568</v>
+        <v>134137510</v>
       </c>
       <c r="B2" t="n">
-        <v>57964</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102119</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,15 +708,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -726,14 +722,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalhygget bakom djurparken, Falköping, Vg</t>
+          <t>Hallastigen, Mösseberg, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>414090</v>
+        <v>414141</v>
       </c>
       <c r="R2" t="n">
-        <v>6450421</v>
+        <v>6450644</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -760,22 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134137503</v>
+        <v>134316896</v>
       </c>
       <c r="B3" t="n">
-        <v>58608</v>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103051</v>
+        <v>100100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,15 +831,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>honfärgad</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -887,22 +887,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,17 +922,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Josefsson</t>
+          <t>Erik Josefsson, Kim Roelofs</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134137510</v>
+        <v>134083568</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>57964</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,21 +940,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102119</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,11 +962,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -976,14 +980,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hallastigen, Mösseberg, Vg</t>
+          <t>Kalhygget bakom djurparken, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414141</v>
+        <v>414090</v>
       </c>
       <c r="R4" t="n">
-        <v>6450644</v>
+        <v>6450421</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1010,22 +1014,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1183,32 +1187,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134316896</v>
+        <v>134137503</v>
       </c>
       <c r="B6" t="n">
-        <v>57860</v>
+        <v>58608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100100</v>
+        <v>103051</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Rosenfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Carpodacus erythrinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1770)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1216,19 +1220,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>honfärgad</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,10 +1307,325 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Josefsson, Kim Roelofs</t>
+          <t>Erik Josefsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>94339116</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nära dammen, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>414315</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6450729</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Friggeråker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Lager</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Lager</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>66577440</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mössebergs östluttning, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>414565</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6451216</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Friggeråker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2012-07-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2012-07-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Carin Franson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carin Franson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>94458070</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>stigkant i kraftledningsgatan N om Mössebergs djurpark, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>414323</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6450912</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Friggeråker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-06-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-06-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>spridda, mest i knopp ännu</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
